--- a/artfynd/A 41628-2024 artfynd.xlsx
+++ b/artfynd/A 41628-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136141635</v>
       </c>
       <c r="B2" t="n">
-        <v>80590</v>
+        <v>80592</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136141640</v>
       </c>
       <c r="B3" t="n">
-        <v>80590</v>
+        <v>80592</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136141666</v>
       </c>
       <c r="B4" t="n">
-        <v>80590</v>
+        <v>80592</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136141667</v>
       </c>
       <c r="B5" t="n">
-        <v>80590</v>
+        <v>80592</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136141668</v>
       </c>
       <c r="B6" t="n">
-        <v>80590</v>
+        <v>80592</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136141651</v>
       </c>
       <c r="B7" t="n">
-        <v>80589</v>
+        <v>80591</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136141660</v>
       </c>
       <c r="B8" t="n">
-        <v>80589</v>
+        <v>80591</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136141636</v>
       </c>
       <c r="B9" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>136141638</v>
       </c>
       <c r="B10" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
         <v>136141639</v>
       </c>
       <c r="B11" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>136141641</v>
       </c>
       <c r="B12" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>136141642</v>
       </c>
       <c r="B13" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         <v>136141643</v>
       </c>
       <c r="B14" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>136141644</v>
       </c>
       <c r="B15" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>136141647</v>
       </c>
       <c r="B16" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         <v>136141648</v>
       </c>
       <c r="B17" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
         <v>136141649</v>
       </c>
       <c r="B18" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
         <v>136141650</v>
       </c>
       <c r="B19" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>136141652</v>
       </c>
       <c r="B20" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
         <v>136141654</v>
       </c>
       <c r="B21" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>136141655</v>
       </c>
       <c r="B22" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3173,7 +3173,7 @@
         <v>136141656</v>
       </c>
       <c r="B23" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3295,7 +3295,7 @@
         <v>136141658</v>
       </c>
       <c r="B24" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>136141659</v>
       </c>
       <c r="B25" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>136141661</v>
       </c>
       <c r="B26" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
         <v>136141663</v>
       </c>
       <c r="B27" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3783,7 +3783,7 @@
         <v>136141665</v>
       </c>
       <c r="B28" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
         <v>136141669</v>
       </c>
       <c r="B29" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4027,7 +4027,7 @@
         <v>136141670</v>
       </c>
       <c r="B30" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         <v>136141671</v>
       </c>
       <c r="B31" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         <v>136141673</v>
       </c>
       <c r="B32" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4393,7 +4393,7 @@
         <v>136141674</v>
       </c>
       <c r="B33" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4510,7 +4510,7 @@
         <v>136141675</v>
       </c>
       <c r="B34" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4632,7 +4632,7 @@
         <v>136141679</v>
       </c>
       <c r="B35" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4754,7 +4754,7 @@
         <v>136141681</v>
       </c>
       <c r="B36" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4876,7 +4876,7 @@
         <v>136141682</v>
       </c>
       <c r="B37" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4998,7 +4998,7 @@
         <v>136141684</v>
       </c>
       <c r="B38" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5120,7 +5120,7 @@
         <v>136141685</v>
       </c>
       <c r="B39" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5242,7 +5242,7 @@
         <v>136141686</v>
       </c>
       <c r="B40" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5364,7 +5364,7 @@
         <v>136141687</v>
       </c>
       <c r="B41" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5486,7 +5486,7 @@
         <v>136141688</v>
       </c>
       <c r="B42" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5608,7 +5608,7 @@
         <v>136141689</v>
       </c>
       <c r="B43" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5730,7 +5730,7 @@
         <v>136141691</v>
       </c>
       <c r="B44" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5852,7 +5852,7 @@
         <v>136141692</v>
       </c>
       <c r="B45" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5974,7 +5974,7 @@
         <v>136141694</v>
       </c>
       <c r="B46" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6096,7 +6096,7 @@
         <v>136141695</v>
       </c>
       <c r="B47" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
         <v>136141697</v>
       </c>
       <c r="B48" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6335,7 +6335,7 @@
         <v>136141698</v>
       </c>
       <c r="B49" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6457,7 +6457,7 @@
         <v>136141699</v>
       </c>
       <c r="B50" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         <v>136141700</v>
       </c>
       <c r="B51" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6701,7 +6701,7 @@
         <v>136141701</v>
       </c>
       <c r="B52" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6823,7 +6823,7 @@
         <v>136141702</v>
       </c>
       <c r="B53" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6945,7 +6945,7 @@
         <v>136141731</v>
       </c>
       <c r="B54" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7067,7 +7067,7 @@
         <v>136141733</v>
       </c>
       <c r="B55" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7189,7 +7189,7 @@
         <v>136141734</v>
       </c>
       <c r="B56" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         <v>136141736</v>
       </c>
       <c r="B57" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         <v>136141742</v>
       </c>
       <c r="B58" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7555,7 +7555,7 @@
         <v>136141678</v>
       </c>
       <c r="B59" t="n">
-        <v>58110</v>
+        <v>58112</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
